--- a/アプリケーション企画実習/設計構成図/フォルダ構成_ファイル一覧.xlsx
+++ b/アプリケーション企画実習/設計構成図/フォルダ構成_ファイル一覧.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tigers\アプリケーション企画実習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tigers\アプリケーション企画実習\設計構成図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0712293A-FD6C-42B1-B5A6-5EB55613E490}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84518D8-97FA-418C-A29E-F2AF61212369}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12420" windowHeight="8715" xr2:uid="{C505DBAB-850C-4C7F-B030-1D70AB873E94}"/>
   </bookViews>
@@ -26,11 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="34">
-  <si>
-    <t>java</t>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="39">
   <si>
     <t>controller</t>
     <phoneticPr fontId="1"/>
@@ -161,6 +157,30 @@
   </si>
   <si>
     <t>event_edit.jsp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hogotaro</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pom.xml</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>src/main/java/com/example/hogotaro/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HogotaroApplication.java</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>config/</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HomeController.java</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -528,326 +548,423 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC4E4481-EE9B-454F-BAF1-0F59A867AD81}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
+      <c r="H3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C11" s="1"/>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="C12" s="1"/>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="D16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" t="s">
+    <row r="21" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+    <row r="24" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="25" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="H25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="26" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
+    <row r="27" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F28" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" t="s">
+      <c r="G28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H29" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" t="s">
+    <row r="30" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" t="s">
+    <row r="31" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" t="s">
+    <row r="32" spans="6:8" x14ac:dyDescent="0.4">
+      <c r="F32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A21" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="1" t="s">
+    <row r="33" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="1"/>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="B43" s="1"/>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="F35" s="1"/>
+      <c r="G35" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G39" s="1"/>
+    </row>
+    <row r="40" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G40" s="1"/>
+    </row>
+    <row r="41" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G41" s="1"/>
+    </row>
+    <row r="42" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G42" s="1"/>
+    </row>
+    <row r="43" spans="6:7" x14ac:dyDescent="0.4">
+      <c r="G43" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -866,92 +983,92 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
